--- a/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caldera</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>106.23</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>91.41</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82.71</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3303</v>
+        <v>3201</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>82.57</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="6">
@@ -567,13 +567,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3201</v>
+        <v>3303</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>82.34</v>
+        <v>86.85</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>74.67</v>
+        <v>79.46</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>65.67</v>
+        <v>70.06</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>57.38</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>47.6</v>
+        <v>50.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:07</t>
+    <t xml:space="preserve">2026-10-05 16:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
